--- a/Excel/Credit Cards.xlsx
+++ b/Excel/Credit Cards.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{2868A320-CD07-4CE9-AB15-8C257570700D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4A565830-4639-4E7D-AB7A-FE97D804D498}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="13_ncr:1_{2868A320-CD07-4CE9-AB15-8C257570700D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12A3C393-47CB-4CD5-9EFA-69C65C8F80B0}"/>
   <bookViews>
-    <workbookView xWindow="3876" yWindow="780" windowWidth="18216" windowHeight="11364" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6780" yWindow="1308" windowWidth="16032" windowHeight="10836" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -211,20 +211,20 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="187" formatCode="&quot;฿&quot;#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="&quot;฿&quot;#,##0.00"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Tahoma"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="14"/>
       <color theme="1"/>
-      <name val="Tahoma"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -253,8 +253,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="187" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="187" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -271,10 +271,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -575,19 +571,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G36"/>
-  <sheetFormatPr defaultColWidth="9.09765625" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.69921875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.59765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.59765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.296875" style="3" customWidth="1"/>
+    <col min="1" max="1" width="11.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.33203125" style="3" customWidth="1"/>
     <col min="5" max="5" width="20" style="2" customWidth="1"/>
-    <col min="6" max="6" width="17.59765625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="16.3984375" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9.09765625" style="2"/>
+    <col min="6" max="6" width="17.5546875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="16.44140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -601,7 +597,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -618,7 +614,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
@@ -629,7 +625,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
@@ -646,7 +642,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>15</v>
       </c>
@@ -660,7 +656,7 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B6" s="1" t="s">
         <v>17</v>
       </c>
@@ -668,7 +664,7 @@
         <v>242881</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B7" s="2" t="s">
         <v>18</v>
       </c>
@@ -676,7 +672,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>20</v>
       </c>
@@ -684,7 +680,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>22</v>
       </c>
@@ -692,7 +688,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>11</v>
       </c>
@@ -703,7 +699,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B12" s="2" t="s">
         <v>25</v>
       </c>
@@ -711,7 +707,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B13" s="2" t="s">
         <v>26</v>
       </c>
@@ -719,7 +715,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>11</v>
       </c>
@@ -736,7 +732,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>11</v>
       </c>
@@ -747,7 +743,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>4</v>
       </c>
@@ -761,7 +757,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>4</v>
       </c>
@@ -772,7 +768,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>15</v>
       </c>
@@ -783,7 +779,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>15</v>
       </c>
@@ -794,7 +790,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>8</v>
       </c>
@@ -805,10 +801,10 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C21" s="3"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>38</v>
       </c>
@@ -823,7 +819,7 @@
         <v>371893.38</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>38</v>
       </c>
@@ -835,10 +831,10 @@
         <v>3603.03</v>
       </c>
       <c r="G23" s="3">
-        <v>619650.9</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+        <v>601650.9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>11</v>
       </c>
@@ -855,10 +851,10 @@
       </c>
       <c r="G24" s="3">
         <f>G22+G23</f>
-        <v>991544.28</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+        <v>973544.28</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>15</v>
       </c>
@@ -866,10 +862,10 @@
         <v>42</v>
       </c>
       <c r="D25" s="3">
-        <v>30000</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+        <v>4930</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>4</v>
       </c>
@@ -881,7 +877,7 @@
       </c>
       <c r="G26" s="3"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
         <v>43</v>
       </c>
@@ -892,7 +888,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
         <v>11</v>
       </c>
@@ -909,7 +905,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>11</v>
       </c>
@@ -926,7 +922,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>4</v>
       </c>
@@ -940,7 +936,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>49</v>
       </c>
@@ -954,7 +950,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
         <v>51</v>
       </c>
@@ -968,7 +964,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B36" s="2" t="s">
         <v>53</v>
       </c>

--- a/Excel/Credit Cards.xlsx
+++ b/Excel/Credit Cards.xlsx
@@ -1,25 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="13_ncr:1_{2868A320-CD07-4CE9-AB15-8C257570700D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12A3C393-47CB-4CD5-9EFA-69C65C8F80B0}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BCA25EC4EDCDF4E3815FBF048E148F5A9AA23115" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF9E3264-7164-4B26-9275-1721CA552D45}"/>
   <bookViews>
-    <workbookView xWindow="6780" yWindow="1308" windowWidth="16032" windowHeight="10836" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1176" windowWidth="14904" windowHeight="10776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -176,12 +173,18 @@
     <t>NAPAPORN</t>
   </si>
   <si>
+    <t>08/29</t>
+  </si>
+  <si>
     <t>4546 3200 5140 9113</t>
   </si>
   <si>
     <t>VISA</t>
   </si>
   <si>
+    <t>07/31</t>
+  </si>
+  <si>
     <t>4050 1630 0229 3121</t>
   </si>
   <si>
@@ -198,12 +201,6 @@
   </si>
   <si>
     <t>0626926112 Dtac Harassment</t>
-  </si>
-  <si>
-    <t>07/31</t>
-  </si>
-  <si>
-    <t>08/29</t>
   </si>
 </sst>
 </file>
@@ -211,21 +208,21 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="&quot;฿&quot;#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="&quot;฿&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -251,11 +248,11 @@
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -316,7 +313,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -349,26 +346,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -401,23 +381,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office 2013 - 2022">
@@ -560,413 +523,408 @@
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G36"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.33203125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="20" style="2" customWidth="1"/>
-    <col min="6" max="6" width="17.5546875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="16.44140625" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9.109375" style="2"/>
+    <col min="1" max="1" width="11.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="25.5546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18.33203125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="20" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.5546875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.44140625" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:5">
+      <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="2">
         <v>30000</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:5">
+      <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:5">
+      <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="2">
         <v>50000</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:5">
+      <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="2">
         <v>250000</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B6" s="1" t="s">
+    <row r="6" spans="1:5">
+      <c r="B6" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="3">
         <v>242881</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B7" s="2" t="s">
+    <row r="7" spans="1:5">
+      <c r="B7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
+    <row r="8" spans="1:5">
+      <c r="A8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
+    <row r="9" spans="1:5">
+      <c r="A9" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" s="2" t="s">
+    <row r="11" spans="1:5">
+      <c r="A11" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="1">
         <v>876</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B12" s="2" t="s">
+    <row r="12" spans="1:5">
+      <c r="B12" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="2">
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B13" s="2" t="s">
+    <row r="13" spans="1:5">
+      <c r="B13" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="2">
         <v>209</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" s="2" t="s">
+    <row r="14" spans="1:5">
+      <c r="A14" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E14" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" s="2" t="s">
+    <row r="15" spans="1:5">
+      <c r="A15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" s="2" t="s">
+    <row r="16" spans="1:5">
+      <c r="A16" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A17" s="2" t="s">
+    <row r="17" spans="1:7">
+      <c r="A17" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A18" s="2" t="s">
+    <row r="18" spans="1:7">
+      <c r="A18" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A19" s="2" t="s">
+    <row r="19" spans="1:7">
+      <c r="A19" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A20" s="2" t="s">
+    <row r="20" spans="1:7">
+      <c r="A20" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="C21" s="3"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A22" s="2" t="s">
+    <row r="21" spans="1:7">
+      <c r="C21" s="2"/>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3">
+      <c r="E22" s="2"/>
+      <c r="F22" s="2">
         <v>3521.94</v>
       </c>
-      <c r="G22" s="3">
+      <c r="G22" s="2">
         <v>371893.38</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A23" s="2" t="s">
+    <row r="23" spans="1:7">
+      <c r="A23" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3">
+      <c r="E23" s="2"/>
+      <c r="F23" s="2">
         <v>3603.03</v>
       </c>
-      <c r="G23" s="3">
-        <v>601650.9</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A24" s="2" t="s">
+      <c r="G23" s="2">
+        <v>631650.9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D24" s="3">
-        <v>50000</v>
-      </c>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3">
+      <c r="D24" s="2">
+        <v>59000</v>
+      </c>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2">
         <f>SUM(F22:F23)</f>
         <v>7124.97</v>
       </c>
-      <c r="G24" s="3">
+      <c r="G24" s="2">
         <f>G22+G23</f>
-        <v>973544.28</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A25" s="2" t="s">
+        <v>1003544.28</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D25" s="3">
-        <v>4930</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A26" s="2" t="s">
+      <c r="D25" s="2">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="2">
         <v>200000</v>
       </c>
-      <c r="G26" s="3"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A27" s="2" t="s">
+      <c r="G26" s="2"/>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B27" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A29" s="2" t="s">
+    <row r="29" spans="1:7">
+      <c r="A29" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B29" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C29" s="2">
+      <c r="C29" s="1">
         <v>212</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D29" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="E29" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C30" s="1">
+        <v>335</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C31" s="1">
+        <v>944</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B32" s="2">
+        <v>300000</v>
+      </c>
+      <c r="C32" s="1">
+        <v>67</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B33" s="2">
+        <v>300000</v>
+      </c>
+      <c r="C33" s="1">
+        <v>68</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="B36" s="1" t="s">
         <v>55</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A30" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C30" s="2">
-        <v>335</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A31" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C31" s="2">
-        <v>944</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A32" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B32" s="3">
-        <v>300000</v>
-      </c>
-      <c r="C32" s="2">
-        <v>67</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B33" s="3">
-        <v>300000</v>
-      </c>
-      <c r="C33" s="2">
-        <v>68</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B36" s="2" t="s">
-        <v>53</v>
       </c>
     </row>
   </sheetData>
